--- a/output_folder/GF-2 PMS2_实测反射率结果.xlsx
+++ b/output_folder/GF-2 PMS2_实测反射率结果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,27 +498,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20231120-REF_样方2_植被（牡丹）-V2.xlsx</t>
+          <t>L-LSR-Z-BYN-M-20221223-样区一小麦-V2.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>巴彦淖尔</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>110°17'08''</t>
+          <t>107°13'23''</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37°30'48''</t>
+          <t>40°43'33''</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>925.6</t>
+          <t>1036.07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,54 +528,54 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>植被,其他</t>
+          <t>植被,耕地,小麦</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-20 10:32:14</t>
+          <t>2022-12-23 11:22:49</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1569200666374431</v>
+        <v>0.2237583442693393</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05816399276390612</v>
+        <v>0.1218130828968888</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07790951798892083</v>
+        <v>0.1655262764029166</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1164580872728641</v>
+        <v>0.221177473514198</v>
       </c>
       <c r="M2" t="n">
-        <v>0.208225757397721</v>
+        <v>0.2487043604320899</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20231120-REF_样方4_水泥地-V2.xlsx</t>
+          <t>L-LSR-Z-BYN-M-20230512-巴彦淖尔站样区1-V2.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>巴彦淖尔</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>110°17'24''</t>
+          <t>107°13'23''</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>37°30'26''</t>
+          <t>40°43'33''</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>960.93</t>
+          <t>1031.5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,54 +585,54 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>水泥路</t>
+          <t>植被,耕地,小麦</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-20 11:34:42</t>
+          <t>2023-05-12 11:41:37</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1915613405233861</v>
+        <v>0.1601406566919809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1194284062197748</v>
+        <v>0.05148339091697989</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1447497318825399</v>
+        <v>0.07981039117219377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1693555346521621</v>
+        <v>0.09852619619012085</v>
       </c>
       <c r="M3" t="n">
-        <v>0.223213259189483</v>
+        <v>0.2200248681705552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20231120-REF_样方5_植被（红薯）-V2.xlsx</t>
+          <t>L-LSR-Z-BYN-M-20231007-巴彦淖尔站样区4-V2.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>巴彦淖尔</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110°17'23''</t>
+          <t>107°13'17''</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37°30'21''</t>
+          <t>40°43'36''</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>952.4</t>
+          <t>1037.95</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -642,54 +642,54 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>水泥路</t>
+          <t>植被,耕地,玉米</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-20 10:00:43</t>
+          <t>2023-10-07 13:37:37</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.223251510723297</v>
+        <v>0.3304406709815831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.124383698774945</v>
+        <v>0.1626500964746563</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1689350546409091</v>
+        <v>0.2147136759831761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2178066192957548</v>
+        <v>0.3033840078540284</v>
       </c>
       <c r="M4" t="n">
-        <v>0.248114413385073</v>
+        <v>0.3886113139906797</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20240702-REF_样方4_水泥地-V2.xlsx</t>
+          <t>L-LSR-Z-DTH-M-20210423-洞庭湖_野外地物光谱仪_1708_XQ-V2.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>洞庭湖</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>110°17'26''</t>
+          <t>113°10'14''</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37°30'25''</t>
+          <t>29°19'09''</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>967.57</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -699,54 +699,54 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>水泥路</t>
+          <t>植被,园地,果园</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-02 09:54:26</t>
+          <t>2021-04-23 10:48:51</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.2722404754174479</v>
+        <v>0.2382472603817278</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1856304614615671</v>
+        <v>0.132649187798926</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2254646559832508</v>
+        <v>0.1777988585221126</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2641658793614522</v>
+        <v>0.2114642314857941</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2961392335275574</v>
+        <v>0.2746600565984447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20240702-REF_样方5_植被（红薯）-V2.xlsx</t>
+          <t>L-LSR-Z-DTH-M-20220421-样区1-水泥路-V2.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>洞庭湖</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>110°17'24''</t>
+          <t>113°10'11''</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37°30'19''</t>
+          <t>29°19'07''</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>948.3</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -756,54 +756,54 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>植被,耕地,其他</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-02 09:41:03</t>
+          <t>2022-04-21 10:39:34</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3343581624682334</v>
+        <v>0.03502098295368027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03846920515604928</v>
+        <v>0.03809178525860793</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07267590178125241</v>
+        <v>0.05921225336661308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06521719470420015</v>
+        <v>0.05184467371821703</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5689241343356113</v>
+        <v>0.02047881394909308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L-LSR-Z-SUD-M-20241029-REF_样方3_植被（草地）-V2.xlsx</t>
+          <t>L-LSR-Z-DTH-M-20220421-样区2-V2.xlsx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>绥德</t>
+          <t>洞庭湖</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>110°17'50''</t>
+          <t>113°10'04''</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37°30'60''</t>
+          <t>29°19'05''</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1000.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -813,85 +813,7495 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>植被,草地,其他</t>
+          <t>水体,湖泊</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-29 10:07:02</t>
+          <t>2022-04-21 11:25:13</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2634106631738772</v>
+        <v>0.1640930631410709</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04401874398141029</v>
+        <v>0.0228362504776859</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07640360475500518</v>
+        <v>0.04511330080087878</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08254954995368785</v>
+        <v>0.04783059851572524</v>
       </c>
       <c r="M7" t="n">
-        <v>0.418261371335913</v>
+        <v>0.2658727461491717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>L-LSR-Z-DTH-M-20220711-2021样区2-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>洞庭湖</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>113°10'06''</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>29°18'54''</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2022-07-11 10:41:46</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.178918123428261</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01906456920601804</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.04046048149755732</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.04138635463630163</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3007359218027267</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-DTH-M-20220914-2021样区2-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>洞庭湖</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>113°10'07''</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>29°19'23''</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2022-09-14 10:58:49</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0217536477113157</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01711771526324486</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02661623783626595</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02312946140195232</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01928080588412883</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-DTH-M-20220914-2021样区3-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>洞庭湖</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>113°10'08''</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>29°19'25''</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>植被,园地,茶园</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2022-09-14 11:20:05</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3190254745666359</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.04961577762157952</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.08679856392733298</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.07615731784527989</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5215514923121465</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20191023-沽源_野外地物光谱仪_138_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>115°38'05''</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>41°46'55''</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1404.15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>沙草地</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2019-10-23 11:26:20</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1555452952187827</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1023171842508778</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1253351110290755</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1521913228165739</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1691428734678002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20200403-沽源_野外地物光谱仪_263_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>115°41'06''</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>41°46'02''</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1389.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2020-04-03 09:59:52</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0837593626577708</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.08066012387809993</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.09465743025242102</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.09888767531175351</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.07325940975022928</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20200810-沽源_野外地物光谱仪_938_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>115°41'10''</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41°45'60''</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1386.53</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2020-08-10 10:27:17</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.06852445619623772</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.05281115275636813</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.07635051143323485</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.07359151440450423</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06405889796990265</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20210731-沽源_野外地物光谱仪_2449_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>115°41'02''</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>41°46'04''</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1392.5</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2021-07-31 09:37:56</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.08514809697626678</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.06356985243519647</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.09026305716048427</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.08632578771525068</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.08360317098524084</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20230806-REF_样方10_植被（草地）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>115°40'45''</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>41°45'52''</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1385.5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>植被,草地,干旱、半干旱草原</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2023-08-06 10:02:09</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1599021933673884</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.03880141187977486</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.05843075263392869</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.06220700823077818</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.248080763049956</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20231028-REF_样方5_植被（土豆）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>115°37'35''</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>41°47'25''</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1407.9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2023-10-28 10:43:55</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2049436355042012</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1113028505778132</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1432107626832425</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1879110016731841</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2383693142568337</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUY-M-20241106-REF_样方15_耕地（裸土）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>沽源</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>115°38'47''</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>41°46'27''</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1393.5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2024-11-06 11:02:43</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1139091180935002</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.06280929330374536</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.08120878570088688</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1069720695199814</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1306915535452821</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20191120-广州_野外地物光谱仪_223_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>113°38'02''</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>23°14'42''</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2019-11-20 11:25:05</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2341379566027448</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.06022752408894608</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.09581646459100067</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1011923871107578</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3501642742558569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20200825-广州_野外地物光谱仪_1056_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>113°38'05''</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>23°14'33''</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2020-08-25 13:26:14</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2606451689747272</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.02310775799487936</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.04431182290326213</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.04426122512884845</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4544071586158007</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20201229-广州_野外地物光谱仪_1399_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>113°38'06''</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>23°14'36''</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2020-12-29 10:17:38</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4507394776915937</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.08266108134120385</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.115106189567547</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1119891568527704</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7395438765713975</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20210123-广州_野外地物光谱仪_1464_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>113°38'02''</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>23°14'42''</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2021-01-23 10:16:42</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2794038826926805</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.06345890491215576</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.09894175173926781</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1448830592901606</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4077068486719372</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20210521-广州_野外地物光谱仪_1907_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>113°38'05''</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>23°14'41''</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>多云</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2021-05-21 09:51:32</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3678979717240437</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.04197028840462213</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0868629092280615</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.07326409766291041</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.622753079477078</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20240714-2024光谱-6-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>113°38'04''</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>23°14'44''</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>31.67</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2024-07-14 14:17:37</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2252218157900754</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0783800186564339</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1251695371197049</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1622411649251835</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2938106236358277</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-GUZ-M-20241219-2024光谱-8-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>113°38'10''</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>23°14'31''</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2024-12-19 11:08:36</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1868174947182211</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.08000289601133266</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1195746536509117</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1676645097701678</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2235599168321576</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-HEB-M-20240507-样区2草地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>126°29'20''</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>45°52'15''</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>107.03</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>植被,草地,其他</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2024-05-07 10:29:29</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1728630674661823</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.06666275540108973</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.08989270463246776</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.113400267871215</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.232098394280377</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-HEB-M-20240509-样区13玉米-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>126°28'11''</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>45°51'19''</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>116.7</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>植被,耕地,玉米</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2024-05-09 12:29:29</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09969482401536091</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.05628840238011262</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.06719739641276373</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0867806295068935</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1193824223189312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-HEB-M-20240903-样区12水体-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>126°28'06''</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>45°51'14''</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>131.3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2024-09-03 09:55:48</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.037306809031548</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0450630540858996</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.06635196847305661</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.05306704245846021</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.02108183262128858</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20200417-栾城_野外地物光谱仪_339_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>114°41'47''</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>37°53'27''</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>植被,草地,其他</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2020-04-17 14:51:07</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3025509657635989</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.08217325469343242</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1275265005616769</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1342193106643468</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4512015866428875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20220825-REF_样方15_植被(小麦）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>114°41'27''</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>37°53'27''</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2022-08-25 11:13:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1974414586661533</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.01903881020132516</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.03497962015990746</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.03792891915307171</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.3477316028510341</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20230130-样区15-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>114°41'28''</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>37°53'26''</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>46.03</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2023-01-30 11:28:45</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1926675260132436</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.07488034947394576</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1052581390915558</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1379090339961016</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2517651810467146</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20230829-REF_样方18_植被（小麦）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>114°43'08''</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>37°53'52''</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>植被,其他</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2023-08-29 12:17:24</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2226701446063027</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0531483546193672</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.1044273651703122</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.09773233629139035</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3229798211228658</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20231129-REF_样方15_植被(小麦）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>114°41'28''</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>37°53'26''</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>41.38</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2023-11-29 11:18:08</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1865525563889273</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.07103103087248115</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.1016061156314673</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1186112733029109</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2502107014469651</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-LUC-M-20241205-REF_样方202412_植被（小麦-玉米）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>栾城</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>114°42'57''</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>37°51'20''</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-62.4</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:45:32</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2580856206495068</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.04036065721026823</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.07622959468651104</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.06393996001315543</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.420532847369127</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20191018-民勤_野外地物光谱仪_56_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>102°55'06''</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>38°37'46''</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1361.7</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2019-10-18 14:45:34</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1909250620219953</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.100778919541832</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.1352003588401674</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1674204583678527</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2241454853525003</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20191030-民勤_野外地物光谱仪_204_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>102°54'51''</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>38°37'45''</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1376.7</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>戈壁</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2019-10-30 12:44:10</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2800719057871591</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.1686514999551596</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2281861698082427</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.283111482445803</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3005560841071681</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20200423-民勤_野外地物光谱仪_366_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>102°55'29''</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>38°24'31''</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1403.17</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2020-04-23 11:34:56</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3069742715530807</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.104395922028208</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.1530447500245098</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1701847047205789</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.4313289510609179</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20200710-民勤_野外地物光谱仪_753_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>102°54'51''</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>38°37'45''</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1368.03</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>戈壁</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2020-07-10 10:20:36</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2782229559070193</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1583968218744105</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2171469577098713</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2794498524634356</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.3026020048003297</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20201029-民勤_野外地物光谱仪_1318_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>102°54'51''</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>38°37'44''</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2020-10-29 10:38:17</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2846374697391884</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1710662457070986</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2320229709880683</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2887583228956066</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.3043532910908106</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20210322-民勤_野外地物光谱仪_1561_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>102°53'12''</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>38°24'54''</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1410.03</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2021-03-22 14:16:38</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.07713204536000168</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.05432123643585469</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.08075546932716848</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.09673315722824324</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.06822893494833179</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20210907-REF_样方9_苜蓿地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>102°58'47''</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>38°34'37''</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1377.5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2021-09-07 11:32:26</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2662594359632141</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.02287942505812833</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.04667563900388912</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.04597830615540964</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.4602065759082421</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20211030-REF_样方11_苜蓿地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>102°58'45''</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>38°34'35''</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2021-10-30 11:45:54</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2692761970896098</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.02799601929771622</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.053537912448962</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.05439986548343125</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.4582146443763802</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20220523-REF_样方25_沙地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>102°50'16''</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>38°36'44''</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1373.63</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2022-05-23 13:46:56</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2647752477327248</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1602765140697401</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2098805962868241</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2657565791621329</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2861920136786211</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20220805-REF_样方4_戈壁-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>102°57'34''</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>38°36'28''</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1371.2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>戈壁</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2022-08-05 12:53:54</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2323322631628263</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1344204155572967</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.1773713405304098</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2136321275284485</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.263681763543332</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20240513-REF_样方4_戈壁-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>102°57'34''</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>38°36'29''</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1342.13</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>戈壁</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2024-05-13 10:26:01</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.2853235646866346</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1633655071543424</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.2167555563677342</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2746863720619856</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.3187932649921375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-MIQ-M-20241106-REF_样方14_土壤（裸沙地）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>民勤</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>102°54'52''</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>38°37'51''</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1382.6</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2024-11-06 10:06:45</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2552760966728742</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.1486075850999548</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.202065556678986</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2574166203755387</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.2756513520061187</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20230613-REF_样方10_植被（草地）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>107°06'26''</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>37°44'21''</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>植被,草地,荒漠草原</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2023-06-13 13:08:11</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2492020396982608</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1187083070054755</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.1639952388209741</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.220171069543015</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.2964090593346644</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20230902-REF_样方1_植被（草地）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>107°08'06''</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>37°43'16''</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1533.1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>植被,草地,荒漠草原</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2023-09-02 11:52:58</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2116189644878498</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.09420790699938496</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.1275389654113644</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1582004050568947</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.269292719075426</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20231120-REF_样方3_草地（禾草）-V2-2.xlsx</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>107°06'29''</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>37°44'11''</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1490.53</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>植被,草地,荒漠草原</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2023-11-20 11:32:43</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.243748528044733</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.1281875074079575</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.174845919711638</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2334539385900482</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.2761780075765432</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20231120-REF_样方3_草地（禾草）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>107°06'29''</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>37°44'11''</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1490.53</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>植被,草地,荒漠草原</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2023-11-20 11:32:43</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.243748528044733</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.1281875074079575</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.174845919711638</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2334539385900482</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.2761780075765432</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20240626-REF_样方11_植被（柠条-V2-2.xlsx</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>107°06'14''</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>37°44'12''</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1499.07</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>植被,林地,灌木林</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2024-06-26 14:39:28</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.238038444079434</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1136932110359384</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.1589768662997635</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2164125316570665</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.2792911757445147</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-NIX-M-20240626-REF_样方11_植被（柠条-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>107°06'14''</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>37°44'12''</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1499.07</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>植被,林地,灌木林</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2024-06-26 14:39:28</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.238038444079434</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.1136932110359384</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.1589768662997635</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2164125316570665</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.2792911757445147</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20191029-祁阳_野外地物光谱仪_185_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>111°49'08''</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>26°44'13''</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2019-10-29 13:55:19</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.04779428542142461</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.02775237084129212</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.05441827561005563</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.04113856243167892</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.04689188003529374</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20191029-祁阳_野外地物光谱仪_189_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>111°52'37''</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>26°45'09''</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>151.58</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2019-10-29 16:01:25</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.01572085486301278</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.01261883508948099</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.01897630546099026</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.01805501276451453</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.01326557011125029</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20191029-祁阳_野外地物光谱仪_190_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>111°48'08''</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>26°40'40''</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>157.4</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2019-10-29 13:03:35</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1103706515012702</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.09148988736923852</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.1007090096955085</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1078700227722616</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1159493509131881</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20191029-祁阳_野外地物光谱仪_193_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>111°52'16''</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>26°45'34''</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>152.43</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>植被,林地,茶园</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2019-10-29 15:10:31</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2267419251881254</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.02243547771413777</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.04626405411657177</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.04333550620981346</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.3889484552179828</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200412-祁阳_野外地物光谱仪_318_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>111°50'46''</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>26°45'10''</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>111.9</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2020-04-12 12:45:10</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2992485222848908</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.06034873088074112</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.1076005591351814</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.08625330202995424</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.4717987951661181</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200412-祁阳_野外地物光谱仪_326_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>111°48'53''</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>26°44'13''</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>98.4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>植被,园地,茶园</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2020-04-12 12:07:28</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.3189793388112306</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.04208994474669352</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.1079748545198794</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.06981060340336709</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.5133162431501601</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200815-祁阳_野外地物光谱仪_984_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>111°52'35''</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>26°45'10''</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>176.08</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2020-08-15 09:51:08</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.07038686224715211</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.04768287497699781</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.1083665089738818</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1031786287126556</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.04438571188785004</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200815-祁阳_野外地物光谱仪_987_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>111°52'16''</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>26°45'35''</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>149.85</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>植被,草地,其他</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2020-08-15 10:20:16</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2962418848439832</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.02304767786383136</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.06011070529905321</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.04994129948904893</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.5086071581822385</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200815-祁阳_野外地物光谱仪_992_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>111°48'09''</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>26°40'44''</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>158.8</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2020-08-15 11:12:43</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1540275196099725</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1333145544893771</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.1431277431730067</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.150948551725123</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.1603383260642359</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20200815-祁阳_野外地物光谱仪_995_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>111°49'07''</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>26°44'12''</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>102.6</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2020-08-15 12:37:13</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1694997454128105</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.109958935351558</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.153790870548696</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.143596087526406</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.1817855431082904</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20201111-祁阳_野外地物光谱仪_1345_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>111°50'47''</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>26°45'25''</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>102.7</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2020-11-11 11:21:15</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5096110191227482</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.05918470930886557</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.1418844760118783</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1040090488409619</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8295180054565129</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20201111-祁阳_野外地物光谱仪_1346_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>111°48'08''</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>26°40'44''</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>164.53</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2020-11-11 09:57:03</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0.1548598943305191</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1286228517920729</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.1416275939851759</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1513724286817268</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.1624227836213307</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20201111-祁阳_野外地物光谱仪_1362_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>111°52'38''</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>26°45'08''</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>157.34</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>植被,草地,其他</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2020-11-11 11:53:36</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0.1051087025048353</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1101650330872113</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.1132963984090473</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1094977031630509</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.09946208393515893</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20210714-祁阳_野外地物光谱仪_2247_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>111°49'07''</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>26°44'12''</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2021-07-14 09:11:29</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1177008911525433</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1101758414151795</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.12774683975656</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.117271643570554</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.1135360187790819</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20210714-祁阳_野外地物光谱仪_2248_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>111°49'17''</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>26°43'57''</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>99.8</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2021-07-14 20:46:16</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2005701307855667</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.0933633897804219</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.1390155314683723</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1904174030903449</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.230406372673762</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20210714-祁阳_野外地物光谱仪_2249_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>111°49'03''</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>26°44'10''</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>105.4</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2021-07-14 09:24:41</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2906708099744742</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.01749196596650299</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.05084266002405714</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.04279288123050774</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.51241079551226</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20210714-祁阳_野外地物光谱仪_2250_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>111°48'55''</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>26°44'42''</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>88.07</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2021-07-14 10:03:05</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0.3752482470279106</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.06461971991289768</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.1111779675278485</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.09349526940528377</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.6101894170393827</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20221023-REF_样方9_水体（水塘）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>111°49'06''</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>26°44'16''</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>110.1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2022-10-23 12:20:33</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0.07507969322726951</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.03202610067726018</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.07020519867471875</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.04463915763237786</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.08977796141544424</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20230703-REF_样方2_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>111°49'09''</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>26°43'29''</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>125.1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2023-07-03 12:54:26</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0.07578100368334154</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.01004157083632826</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.01982358792686189</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.01690735960748525</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.1281937226214337</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20241025-REF_样方10_植被（烟草）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>111°57'02''</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>26°46'21''</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2024-10-25 10:48:30</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0.175823052803651</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.06625926127161956</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.09560232513975911</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1319605610515294</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.2269922576325523</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20241025-REF_样方5_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>111°57'46''</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>26°42'58''</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>155.03</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2024-10-25 12:13:33</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0.2057019537262139</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.02144170155070939</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.04831755827124148</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.047938103927927</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.3470090197389354</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20241129-REF_样方10_植被（烟草）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>111°57'03''</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>26°46'20''</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2024-11-29 10:41:35</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0.115428933573691</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.0486314434470647</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.07187184083417555</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1011628711315569</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.1397277017028553</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20241129-REF_样方14_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>111°57'11''</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>26°43'17''</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2024-11-29 12:34:29</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0.1572103227120208</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.05803867879663174</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.08257020613101718</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1112097028377757</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.2075030840427531</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-QIY-M-20241129-REF_样方7_植被（烟草）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>祁阳</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>111°58'03''</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>26°45'20''</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>144.53</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2024-11-29 11:07:05</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0.08720160747205541</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.03655121380426669</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.05612115058614434</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.07996891026065989</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1029037264757129</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SHQ-M-20221212-REF_样方4_植被（小麦）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>115°35'45''</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>34°30'58''</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2022-12-12 10:57:02</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0.2472144629673885</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.05109720066983608</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.09092494717222585</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.07897252234655178</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.3858481182163005</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SHQ-M-20230313-样区10-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>115°32'48''</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>34°31'19''</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>45.68</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2023-03-13 10:39:35</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.1868805434297512</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.02246297704330089</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.03633307172461941</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.04024554363554127</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.3229529031588455</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SHQ-M-20231107-REF2_样方1_植被（小麦）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>115°35'30''</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>34°31'15''</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>56.15</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2023-11-07 10:09:58</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1556387600556494</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.05021891264358574</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.08030175158519383</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.09022445470481723</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.2146773243798911</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SHQ-M-20240625-REF3_样方1_植被（小麦-玉米）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>115°35'30''</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>34°31'15''</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>植被,耕地,玉米</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2024-06-25 09:39:07</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0.2288417855128535</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.09447676945457034</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.1348027057619945</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1969841955951598</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.2818987081263001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SHQ-M-20241024-REF3_样方1_植被（小麦-玉米）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>115°35'30''</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>34°31'14''</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2024-10-24 10:07:11</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0.1919039353102997</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.07867804212068243</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.1100828063388908</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1659515701238106</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.2367993879606333</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20231120-REF_样方2_植被（牡丹）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>110°17'08''</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>37°30'48''</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>925.6</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>植被,其他</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2023-11-20 10:32:14</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0.1569200666374431</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.05816399276390612</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.07790951798892083</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1164580872728641</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.208225757397721</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20231120-REF_样方4_水泥地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>110°17'24''</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>37°30'26''</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>960.93</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2023-11-20 11:34:42</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0.1915613405233861</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.1194284062197748</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.1447497318825399</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1693555346521621</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.223213259189483</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20231120-REF_样方5_植被（红薯）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>110°17'23''</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>37°30'21''</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>952.4</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2023-11-20 10:00:43</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0.223251510723297</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.124383698774945</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.1689350546409091</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.2178066192957548</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.248114413385073</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20240702-REF_样方4_水泥地-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>110°17'26''</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>37°30'25''</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>967.57</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2024-07-02 09:54:26</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2722404754174479</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.1856304614615671</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.2254646559832508</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.2641658793614522</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.2961392335275574</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20240702-REF_样方5_植被（红薯）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>110°17'24''</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>37°30'19''</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>948.3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2024-07-02 09:41:03</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0.3343581624682334</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.03846920515604928</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.07267590178125241</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.06521719470420015</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.5689241343356113</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-SUD-M-20241029-REF_样方3_植被（草地）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>绥德</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>110°17'50''</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>37°30'60''</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1000.3</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>植被,草地,其他</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2024-10-29 10:07:02</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0.2634106631738772</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.04401874398141029</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.07640360475500518</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.08254954995368785</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.418261371335913</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>L-LSR-Z-SUD-M-20241029-REF_样方4_水泥地-V2.xlsx</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>绥德</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>110°17'24''</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>37°30'25''</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>961.95</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>水泥路</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2024-10-29 09:46:19</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I87" t="n">
         <v>0.2103449796825804</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J87" t="n">
         <v>0.1340539823403412</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K87" t="n">
         <v>0.1621475521737675</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L87" t="n">
         <v>0.1891310333427449</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M87" t="n">
         <v>0.2417315151387523</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-WEC-M-20221219-REF_样方1_植被（地瓜）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>文昌</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>110°45'46''</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>19°32'25''</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>32.05</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2022-12-19 10:26:26</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0.2813931016169612</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.1140925043348975</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.1879921731899763</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.2587912049831308</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.3281840993374108</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-WEC-M-20230223-REF_样方6_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>文昌</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>110°49'15''</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>19°38'30''</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2023-02-23 10:04:57</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0.2093546521996646</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.02304399115851476</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.04876378625180607</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.0401931640868966</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.3575128615775788</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-WEC-M-20231211-REF_样方16_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>文昌</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>110°44'25''</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>19°32'05''</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>16.23</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2023-12-11 11:22:50</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0.08605208525403213</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.02944795028508491</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.04265077855523132</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.05175004669998173</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.118994228252256</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-WEC-M-20240712-REF_样方12_植被（水稻）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>文昌</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>110°45'42''</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>19°36'48''</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>13.27</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2024-07-12 10:38:54</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0.1508612851971622</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.04243397071551275</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.0680458599492362</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.08046254055594225</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.2167408731269672</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-WEC-M-20241108-REF_样方4_土壤（沙滩）-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>文昌</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>110°48'23''</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>19°31'31''</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-6.85</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>沙地</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2024-11-08 10:35:24</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0.2239459785986336</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1442713165773472</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.185701210229688</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.221446171813082</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.2422504656457723</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20191019-锡林浩特_野外地物光谱仪_64_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>44°07'51''</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1101.4</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2019-10-19 18:36:25</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0.0299615600501961</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.02851783906550025</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.03383277983855667</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.03384599553194301</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.02676355717941794</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20191019-锡林浩特_野外地物光谱仪_65_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>116°19'40''</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>44°08'10''</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1109.95</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2019-10-19 19:28:07</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0.1985459274092533</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.08411209578091133</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.1135929567416104</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1592123798882351</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.2497495675173098</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20200723-锡林浩特_野外地物光谱仪_810_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>116°19'48''</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>44°08'18''</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1047.5</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2020-07-23 10:11:40</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0.1505866076275026</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.04220789270758353</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.06843371948391377</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.07142815303310403</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.2204404496163594</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20200723-锡林浩特_野外地物光谱仪_831_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>116°19'23''</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>44°08'27''</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1128.9</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2020-07-23 10:01:06</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0.1505966722646899</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.0445804066756142</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.06854123462660357</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.07990413698476326</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.2173500337647601</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20200723-锡林浩特_野外地物光谱仪_834_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>44°07'53''</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1103.7</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2020-07-23 10:45:17</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0.04129674895318385</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.026369496407149</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.04224365362353311</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.0359024480350669</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.04297994092759654</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20201116-锡林浩特_野外地物光谱仪_1373_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>116°19'25''</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>44°08'28''</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1125.9</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2020-11-16 09:13:18</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0.1937114139550626</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.08161431194107942</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.1125379275866844</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1695902115504522</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.237294784123201</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20201116-锡林浩特_野外地物光谱仪_1375_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>116°19'40''</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>44°08'09''</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1110.4</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2020-11-16 09:59:55</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2118948472206363</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.08900511536108111</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.1232672280246312</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1870137980737344</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.2585966755249022</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20201116-锡林浩特_野外地物光谱仪_1376_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>116°19'54''</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>44°07'51''</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1106.27</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2020-11-16 10:16:08</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0.05056849994232944</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.05126973495287715</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.06347473075921631</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.06571576060335843</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.03847137211101598</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20210728-锡林浩特_野外地物光谱仪_2418_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>44°07'51''</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1091.07</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>多云</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>水塘</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2021-07-28 11:09:49</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0.08917839613028049</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.07005572884029071</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.09230261930350733</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.09298219366107126</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.08593634271196147</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20210728-锡林浩特_野外地物光谱仪_2427_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>116°19'23''</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>44°08'28''</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1124.38</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2021-07-28 10:03:50</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0.133684393348677</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.03499994633272833</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.05728295914634193</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.06160205695750269</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.198724850341417</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20210728-锡林浩特_野外地物光谱仪_2428_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>116°19'49''</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>44°08'18''</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1105.9</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2021-07-28 10:24:11</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0.1608850006315268</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.03772430879405096</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.06457540864799108</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.06615159111408989</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.2446222914132393</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20210728-锡林浩特_野外地物光谱仪_2430_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>44°07'51''</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1091.07</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2021-07-28 11:09:49</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0.09699266865860307</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.08085688153778146</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.104530584479246</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.1146870391615643</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.0862159858442836</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20211021-锡林浩特_野外地物光谱仪_3175_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>116°19'25''</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>44°08'27''</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1131.6</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2021-10-21 09:47:32</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0.1686680016636819</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.06632786693032219</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.0915181653624709</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.138996376353216</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.2129679708334764</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20211021-锡林浩特_野外地物光谱仪_3176_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>116°19'47''</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>44°08'19''</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1104.33</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2021-10-21 10:10:40</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0.1820845439160738</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.07346323858841744</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.1002700066684006</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.1542002300464607</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.2277380032373822</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20211021-锡林浩特_野外地物光谱仪_3178_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>116°19'41''</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>44°08'08''</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1111.38</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2021-10-21 10:29:29</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0.147102379013198</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.06003642649811576</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.08118343107169285</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.1220657653795377</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.1851431205539969</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20220523-样区6-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>116°19'40''</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>44°08'09''</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1105.57</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>积云</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2022-05-23 14:40:12</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0.2019842398382425</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.08849800560941945</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.1242988426384094</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.1710399411244266</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.248286252752235</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20220523-样区7-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>116°19'52''</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>44°07'56''</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1102.5</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2022-05-23 14:50:34</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0.2271915876332401</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.1022831626175279</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.1430152356016807</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.2020263917683169</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.2733480283450561</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20221110-样区1-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>116°19'25''</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>44°08'27''</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1125.8</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2022-11-10 09:42:00</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0.2669868887741649</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.09980318112972013</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.1457704757855608</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.2312131358504463</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.3323875041011442</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20221110-样区2-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>116°19'22''</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>44°08'21''</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1120.07</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2022-11-10 10:15:30</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0.2453602479242387</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.08772178297298266</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.1289774696930421</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.2079687815174427</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.3094426351944182</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20230730-样区1-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>116°19'23''</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>44°08'27''</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1117.5</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2023-07-30 09:54:04</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0.1666443536775384</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.05228873950976582</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.08100522308155775</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.09126147116474971</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.2365518544427382</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20230730-样区4-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>44°07'54''</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1100.2</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2023-07-30 11:07:30</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0.0345221513324423</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.02730587521618906</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.04265104301346781</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.04619908040221311</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.0267431202000686</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20231023-样区5-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>116°19'26''</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>44°08'19''</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1071.45</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2023-10-23 09:38:23</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0.1387824366000787</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.06634190271367411</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.08999894779104857</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.129562121615887</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.1625430869750491</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20240521-地物光谱样区2-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>116°19'48''</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>44°08'18''</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1105.43</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2024-05-21 10:05:44</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0.1855889198885656</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.08764601263375642</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.1194563107545394</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.1609985325407897</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.2241181829338603</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20240521-地物光谱样区4-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>116°19'55''</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>44°07'53''</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1110.23</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>水体,其他</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2024-05-21 10:37:55</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0.02892773604947824</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.02605205295654819</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.03579929967396629</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.03795302057197138</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.02247603961130179</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-XLH-M-20241101-地物光谱样区2-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>锡林浩特</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>116°19'48''</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>44°08'18''</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1097.8</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>植被,草地,典型草原</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2024-11-01 10:50:24</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0.1775888787473508</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.06990280100904439</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.0967744192456205</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.1543037153172645</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.2206519618688264</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20230906-REF_样方12_滩涂-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>120°56'57''</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>32°41'24''</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>薄云</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>盐碱地</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2023-09-06 10:22:16</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0.1077295973693571</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.05816768981790568</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.07782314734139205</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.09347070294307395</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.1266928936682581</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20231206-REF_样方05_大豆-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>120°55'06''</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>32°39'14''</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>薄云</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2023-12-06 10:41:52</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0.2405230076337926</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.05447593681073211</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.07233040389478138</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.09850176424132666</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.3644137321173301</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20240508-REF_样方73-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>120°29'09''</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>33°48'25''</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-5.3</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>盐碱地</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2024-05-08 10:01:57</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0.1250375371441296</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.06970496596997344</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.09427731168936419</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.1198889125526584</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.140205876006174</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20240508-REF_样方75-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>120°25'50''</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>33°47'34''</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2024-05-08 11:47:45</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0.2214032893567998</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.01704237921163844</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.02952738561086491</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.03751509115628645</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.4019078464577617</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20240730-REF_样方89-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>120°23'12''</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>33°58'36''</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2024-07-30 09:49:57</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2046516651750707</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.01856887155445139</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.03841168158921612</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.03724226854658051</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.358073341253069</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20240822-REF_样方85-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>120°23'35''</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>33°44'52''</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>植被,耕地,水稻</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2024-08-22 09:45:34</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0.170177035516334</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.01273553430863109</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.02556532024713591</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.02669012867242979</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.3047465154254342</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20241024-REF_样方88-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>120°23'43''</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>33°45'49''</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>植被,耕地,其他</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2024-10-24 11:05:28</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0.1141348491444308</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.04381586117677364</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.06030911290146777</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.08539243392031019</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.1492403241487759</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20241129-REF_样方90-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>120°23'18''</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>33°57'50''</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2024-11-29 09:29:45</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0.1592208831536842</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.08521891821830685</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.1168862367832484</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.1519775888692935</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.180126445239682</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YAC-M-20241231-REF_样方89-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>盐城</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>120°23'13''</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>33°58'35''</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2024-12-31 09:31:47</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0.1977109447533392</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.08911149046315008</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.1262403607313111</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.1550156225032757</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.2450532243399326</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20191020-禹城_野外地物光谱仪_98_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>118°55'40''</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>37°39'38''</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-5.2</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2019-10-20 11:33:24</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0.07146294113917345</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.05844719795354318</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.08276936249070886</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.092160783440653</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.05918979985708375</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20191020-禹城_野外地物光谱仪_99_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>118°55'16''</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>37°40'09''</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2019-10-20 10:50:46</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0.2386567740180551</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.1227216878499992</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.1702601889333143</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.2271268749451851</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.2716869924800854</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20200427-禹城_野外地物光谱仪_388_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>118°55'23''</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>37°40'06''</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2020-04-27 10:47:52</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2765824346416603</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.157246030080732</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.2109309762550096</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2700035799525081</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3067160363675489</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20200427-禹城_野外地物光谱仪_391_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>118°55'33''</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>37°42'04''</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2020-04-27 10:19:29</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3559924327503258</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3113130021768332</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3441582836050242</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3671780350144155</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3565089540056013</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20200907-禹城_野外地物光谱仪_1094_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>118°55'15''</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>37°40'08''</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2020-09-07 09:17:30</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0.1802211426062633</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.04041201205723464</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.06129053212113854</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.08351711651801128</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.2669772705120033</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20200907-禹城_野外地物光谱仪_1095_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>118°55'03''</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>37°40'12''</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2020-09-07 09:44:14</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0.1931435808704568</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.03482463758352503</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.06473458412063758</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.0612408300834057</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3065113292095967</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20200907-禹城_野外地物光谱仪_1096_XQ-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>118°55'12''</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>37°40'28''</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>水体,湖泊</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2020-09-07 20:29:35</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0.2466024554023389</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.06745460121399349</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.1081630804643175</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.1087891052079178</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3626619253044934</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20230906-禹城水泥样区1-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>116°34'22''</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>36°49'51''</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2023-09-06 10:59:32</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0.1471848925289905</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.1271636601637103</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.1452803919185991</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.1550141392832256</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.1446984832048633</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20240319-禹城水泥样区1-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>116°34'22''</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>36°49'50''</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>103.7</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2024-03-19 11:05:17</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3462366253145822</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.2591983219328263</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3137762712960308</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3573461818699387</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3556463191014044</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20240319-禹城野外地物光谱农田样区-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>116°34'19''</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>36°49'50''</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>植被,耕地,小麦</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2024-03-19 11:14:52</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1928160228675473</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.03386497614382484</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.05493308871698236</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.06488279618803033</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3104976756378054</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20240828-禹城水泥样区1-V2-2.xlsx</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>116°34'21''</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>36°49'52''</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>水泥路</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2024-08-28 10:32:14</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0.3536136772340235</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2571682780007814</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3149825001041408</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3621867735952755</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3664790562307132</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>L-LSR-Z-YUC-M-20240828-禹城水泥样区1-V2.xlsx</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>禹城</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>116°34'22''</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>36°49'51''</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>裸地</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2024-08-28 10:35:54</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3522235653033742</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2580286530714836</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3151531692104844</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3610364206049624</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3644391616358708</v>
       </c>
     </row>
   </sheetData>
